--- a/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
+++ b/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4214,6 +4214,53 @@
         </is>
       </c>
       <c r="K74" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>מוצרי צריכה נוספים</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>קסדות</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>חסר</t>
         </is>

--- a/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
+++ b/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="דרישות יבוא" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דרישות יבוא" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'דרישות יבוא'!$1:$1</definedName>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>לבדוק</t>
+          <t>כן</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>לבדוק</t>
+          <t>כן</t>
         </is>
       </c>
       <c r="I38" s="4" t="n"/>

--- a/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
+++ b/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
@@ -2503,7 +2503,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>כן</t>
+          <t>לבדוק</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>לבדוק</t>
+          <t>כן</t>
         </is>
       </c>
       <c r="I39" s="4" t="n"/>

--- a/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
+++ b/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="דרישות יבוא" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דרישות יבוא" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'דרישות יבוא'!$1:$1</definedName>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>לבדוק</t>
+          <t>כן</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>לבדוק</t>
+          <t>כן</t>
         </is>
       </c>
       <c r="I38" s="4" t="n"/>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>כן</t>
+          <t>לבדוק</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>לבדוק</t>
+          <t>כן</t>
         </is>
       </c>
       <c r="I39" s="4" t="n"/>

--- a/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
+++ b/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4261,6 +4261,288 @@
         </is>
       </c>
       <c r="K75" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>מוצרי צריכה נוספים</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>מכשירי גז ואביזרי גז</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>חשמל ואלקטרוניקה</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>מזגנים ומקררים</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>חשמל ואלקטרוניקה</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>פאנלים סולאריים</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>חשמל ואלקטרוניקה</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ממירים סולאריים</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>רכב ותחבורה</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>עמדות טעינה לרכב חשמלי</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>מוצרי צריכה נוספים</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>מוצרי טבק וסיגריות אלקטרוניות</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>חסר</t>
         </is>

--- a/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
+++ b/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4543,6 +4543,476 @@
         </is>
       </c>
       <c r="K81" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>בריאות ותמרוקים</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>אמצעים למניעת הריון</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>בריאות ותמרוקים</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>עדשות מגע ומשקפיים</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>בריאות ותמרוקים</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>מתכלים רפואיים</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>כימיקלים וחומרים</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>דשנים</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ילדים ותינוקות</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>מושבי בטיחות לילדים</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>בנייה ותעשייה</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ציוד כיבוי אש</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>מוצרי צריכה נוספים</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>נשק וציוד ביטחוני</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>כימיקלים וחומרים</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>טרפנטין וחומרים דליקים להצתת פחמים או עץ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>בנייה ותעשייה</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>מעליות וציוד הרמה</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>חסר</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>בריאות ותמרוקים</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>מכשירי רנטגן</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>לבדוק</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>חסר</t>
         </is>

--- a/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
+++ b/data/FreighTime_Simple_Import_Requirements_Matrix.xlsx
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>לבדוק</t>
+          <t>כן</t>
         </is>
       </c>
       <c r="I40" s="4" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>לבדוק</t>
+          <t>כן</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
